--- a/2026.05.16_陆啸.xlsx
+++ b/2026.05.16_陆啸.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luxiao/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luxiao/code/chat-flask/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36ED68F-9271-9D42-B986-B585575CFD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C38747-B095-664B-BD7C-B65B0BC970CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="21040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="111">
   <si>
     <t>微信昵称</t>
   </si>
@@ -353,14 +353,6 @@
   </si>
   <si>
     <t>2026-04-21 18:21:02</t>
-  </si>
-  <si>
-    <t>桌号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>位置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -736,12 +728,8 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>112</v>
-      </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" ht="60" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -756,9 +744,6 @@
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="60" customHeight="1">
@@ -774,9 +759,6 @@
       <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -791,9 +773,6 @@
       <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
     </row>
     <row r="5" spans="1:6" ht="60" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -808,9 +787,6 @@
       <c r="D5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1">
       <c r="A6" s="1" t="s">
@@ -825,9 +801,6 @@
       <c r="D6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1">
       <c r="A7" s="1" t="s">
@@ -842,9 +815,6 @@
       <c r="D7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1">
       <c r="A8" s="1" t="s">
@@ -859,9 +829,6 @@
       <c r="D8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1">
       <c r="A9" s="1" t="s">
@@ -876,9 +843,6 @@
       <c r="D9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
     </row>
     <row r="10" spans="1:6" ht="60" customHeight="1">
       <c r="A10" s="1" t="s">
@@ -893,9 +857,6 @@
       <c r="D10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
     </row>
     <row r="11" spans="1:6" ht="60" customHeight="1">
       <c r="A11" s="1" t="s">
@@ -910,9 +871,6 @@
       <c r="D11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
     </row>
     <row r="12" spans="1:6" ht="60" customHeight="1">
       <c r="A12" s="1" t="s">
@@ -927,9 +885,6 @@
       <c r="D12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E12">
-        <v>3</v>
-      </c>
     </row>
     <row r="13" spans="1:6" ht="60" customHeight="1">
       <c r="A13" s="1" t="s">
@@ -943,9 +898,6 @@
       </c>
       <c r="D13" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="E13">
-        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="60" customHeight="1">
@@ -959,9 +911,6 @@
       <c r="D14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E14">
-        <v>5</v>
-      </c>
     </row>
     <row r="15" spans="1:6" ht="60" customHeight="1">
       <c r="A15" s="1" t="s">
@@ -976,9 +925,6 @@
       <c r="D15" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E15">
-        <v>5</v>
-      </c>
     </row>
     <row r="16" spans="1:6" ht="60" customHeight="1">
       <c r="A16" s="1" t="s">
@@ -993,11 +939,8 @@
       <c r="D16" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15">
+    </row>
+    <row r="17" spans="1:4" ht="15">
       <c r="A17" s="1" t="s">
         <v>40</v>
       </c>
@@ -1010,11 +953,8 @@
       <c r="D17" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15">
+    </row>
+    <row r="18" spans="1:4" ht="15">
       <c r="A18" s="1" t="s">
         <v>56</v>
       </c>
@@ -1027,11 +967,8 @@
       <c r="D18" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15">
+    </row>
+    <row r="19" spans="1:4" ht="15">
       <c r="A19" s="1" t="s">
         <v>58</v>
       </c>
@@ -1044,11 +981,8 @@
       <c r="D19" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15">
+    </row>
+    <row r="20" spans="1:4" ht="15">
       <c r="A20" s="1" t="s">
         <v>61</v>
       </c>
@@ -1061,11 +995,8 @@
       <c r="D20" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15">
+    </row>
+    <row r="21" spans="1:4" ht="15">
       <c r="A21" s="1" t="s">
         <v>64</v>
       </c>
@@ -1078,11 +1009,8 @@
       <c r="D21" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15">
+    </row>
+    <row r="22" spans="1:4" ht="15">
       <c r="A22" s="1" t="s">
         <v>67</v>
       </c>
@@ -1095,11 +1023,8 @@
       <c r="D22" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15">
+    </row>
+    <row r="23" spans="1:4" ht="15">
       <c r="A23" s="1" t="s">
         <v>70</v>
       </c>
@@ -1112,11 +1037,8 @@
       <c r="D23" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15">
+    </row>
+    <row r="24" spans="1:4" ht="15">
       <c r="A24" s="1" t="s">
         <v>72</v>
       </c>
@@ -1129,11 +1051,8 @@
       <c r="D24" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15">
+    </row>
+    <row r="25" spans="1:4" ht="15">
       <c r="A25" s="1" t="s">
         <v>75</v>
       </c>
@@ -1146,11 +1065,8 @@
       <c r="D25" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15">
+    </row>
+    <row r="26" spans="1:4" ht="15">
       <c r="A26" s="1" t="s">
         <v>78</v>
       </c>
@@ -1163,11 +1079,8 @@
       <c r="D26" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15">
+    </row>
+    <row r="27" spans="1:4" ht="15">
       <c r="A27" s="1" t="s">
         <v>72</v>
       </c>
@@ -1180,11 +1093,8 @@
       <c r="D27" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15">
+    </row>
+    <row r="28" spans="1:4" ht="15">
       <c r="A28" s="1" t="s">
         <v>81</v>
       </c>
@@ -1197,11 +1107,8 @@
       <c r="D28" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="15">
+    </row>
+    <row r="29" spans="1:4" ht="15">
       <c r="A29" s="1" t="s">
         <v>84</v>
       </c>
@@ -1214,11 +1121,8 @@
       <c r="D29" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E29">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="15">
+    </row>
+    <row r="30" spans="1:4" ht="15">
       <c r="A30" s="1" t="s">
         <v>87</v>
       </c>
@@ -1231,11 +1135,8 @@
       <c r="D30" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E30">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15">
+    </row>
+    <row r="31" spans="1:4" ht="15">
       <c r="A31" s="1" t="s">
         <v>91</v>
       </c>
@@ -1248,11 +1149,8 @@
       <c r="D31" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15">
+    </row>
+    <row r="32" spans="1:4" ht="15">
       <c r="A32" s="1" t="s">
         <v>93</v>
       </c>
@@ -1265,11 +1163,8 @@
       <c r="D32" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E32">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15">
+    </row>
+    <row r="33" spans="1:4" ht="15">
       <c r="A33" s="1" t="s">
         <v>96</v>
       </c>
@@ -1282,11 +1177,8 @@
       <c r="D33" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E33">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="15">
+    </row>
+    <row r="34" spans="1:4" ht="15">
       <c r="A34" s="1" t="s">
         <v>100</v>
       </c>
@@ -1299,11 +1191,8 @@
       <c r="D34" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E34">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15">
+    </row>
+    <row r="35" spans="1:4" ht="15">
       <c r="A35" s="1" t="s">
         <v>103</v>
       </c>
@@ -1316,11 +1205,8 @@
       <c r="D35" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E35">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="15">
+    </row>
+    <row r="36" spans="1:4" ht="15">
       <c r="A36" s="1" t="s">
         <v>105</v>
       </c>
@@ -1333,11 +1219,8 @@
       <c r="D36" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E36">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="15">
+    </row>
+    <row r="37" spans="1:4" ht="15">
       <c r="A37" s="1" t="s">
         <v>108</v>
       </c>
@@ -1349,9 +1232,6 @@
       </c>
       <c r="D37" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="E37">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
